--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/damolaogundipe/Documents/sai360-coverage-site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBCC8FB-7A8A-B04A-BA2B-85E9E7FCA350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1F4AAC-EDB7-C848-90E5-8AB17F9B36B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43540" yWindow="3260" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regulatory Coverage - Other" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Exchanges!$A$1:$E$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Regulatory Coverage - Other'!$A$1:$C$1</definedName>
   </definedNames>
-  <calcPr calcId="0" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3826" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5437" uniqueCount="1652">
   <si>
     <t>Region</t>
   </si>
@@ -3398,6 +3398,1593 @@
   </si>
   <si>
     <t>SUBS_PL_LC_IJ</t>
+  </si>
+  <si>
+    <t>European Chemicals Agency</t>
+  </si>
+  <si>
+    <t>European Commission - DG Environment</t>
+  </si>
+  <si>
+    <t>European Commission - DG TAXUD</t>
+  </si>
+  <si>
+    <t>Revenue and Customs</t>
+  </si>
+  <si>
+    <t>Administration for Children and Families (ACF)</t>
+  </si>
+  <si>
+    <t>Administration for Community Living (ACL)</t>
+  </si>
+  <si>
+    <t>Administration for Strategic Preparedness and Response (ASPR)</t>
+  </si>
+  <si>
+    <t>Advanced Research Projects Agency for Health (ARPA-H)</t>
+  </si>
+  <si>
+    <t>Agency for Healthcare Research and Quality (AHRQ)</t>
+  </si>
+  <si>
+    <t>Agency for Toxic Substances and Disease Registry (ATSDR)</t>
+  </si>
+  <si>
+    <t>Biomedical Advanced Research and Development Authority (BARDA)</t>
+  </si>
+  <si>
+    <t>Centers for Disease Control and Prevention (CDC)</t>
+  </si>
+  <si>
+    <t>Centers for Medicare &amp; Medicaid Services (CMS)</t>
+  </si>
+  <si>
+    <t>Consumer Financial Protection Bureau (CFPB)</t>
+  </si>
+  <si>
+    <t>Consumer Product Safety Commission (CPSC)</t>
+  </si>
+  <si>
+    <t>Cybersecurity and Infrastructure Security Agency (CISA)</t>
+  </si>
+  <si>
+    <t>Defense Health Agency (DHA)</t>
+  </si>
+  <si>
+    <t>Departmental Appeals Board (HHS DAB)</t>
+  </si>
+  <si>
+    <t>Drug Enforcement Administration (DEA)</t>
+  </si>
+  <si>
+    <t>Employee Benefits Security Administration (EBSA)</t>
+  </si>
+  <si>
+    <t>Environmental Protection Agency (EPA)</t>
+  </si>
+  <si>
+    <t>Equal Employment Opportunity Commission (EEOC)</t>
+  </si>
+  <si>
+    <t>Federal Communications Commission (FCC)</t>
+  </si>
+  <si>
+    <t>Federal Trade Commission (FTC)</t>
+  </si>
+  <si>
+    <t>Food and Drug Administration (FDA)</t>
+  </si>
+  <si>
+    <t>Health Resources and Services Administration (HRSA)</t>
+  </si>
+  <si>
+    <t>Indian Health Service (IHS)</t>
+  </si>
+  <si>
+    <t>Internal Revenue Service (IRS)</t>
+  </si>
+  <si>
+    <t>National Institute for Occupational Safety and Health (NIOSH)</t>
+  </si>
+  <si>
+    <t>National Institutes of Health (NIH)</t>
+  </si>
+  <si>
+    <t>Nuclear Regulatory Commission (NRC)</t>
+  </si>
+  <si>
+    <t>Occupational Safety and Health Administration (OSHA)</t>
+  </si>
+  <si>
+    <t>Office for Civil Rights (HHS OCR)</t>
+  </si>
+  <si>
+    <t>Office for Human Research Protections (OHRP)</t>
+  </si>
+  <si>
+    <t>Office of Inspector General (HHS OIG)</t>
+  </si>
+  <si>
+    <t>Office of Medicare Hearings and Appeals (OMHA)</t>
+  </si>
+  <si>
+    <t>Office of Personnel Management (OPM)</t>
+  </si>
+  <si>
+    <t>Office of the Assistant Secretary for Health (OASH)</t>
+  </si>
+  <si>
+    <t>Office of the Assistant Secretary for Technology Policy / Office of the National Coordinator for Health IT (ASTP/ONC)</t>
+  </si>
+  <si>
+    <t>Office of the National Drug Control Policy (ONDCP)</t>
+  </si>
+  <si>
+    <t>Social Security Administration (SSA)</t>
+  </si>
+  <si>
+    <t>Substance Abuse and Mental Health Services Administration (SAMHSA)</t>
+  </si>
+  <si>
+    <t>U.S. Department of Agriculture, Food Safety and Inspection Service (USDA FSIS)</t>
+  </si>
+  <si>
+    <t>U.S. Department of Defense (DoD)</t>
+  </si>
+  <si>
+    <t>U.S. Department of Health and Human Services (HHS)</t>
+  </si>
+  <si>
+    <t>U.S. Department of Justice (DOJ)</t>
+  </si>
+  <si>
+    <t>U.S. Department of Labor (DOL)</t>
+  </si>
+  <si>
+    <t>U.S. Department of the Treasury</t>
+  </si>
+  <si>
+    <t>U.S. Department of Transportation (DOT)</t>
+  </si>
+  <si>
+    <t>U.S. Department of Veterans Affairs, Veterans Health Administration (VHA)</t>
+  </si>
+  <si>
+    <t>Alabama Department of Public Health</t>
+  </si>
+  <si>
+    <t>Alabama Medicaid Agency</t>
+  </si>
+  <si>
+    <t>Alabama Department of Insurance</t>
+  </si>
+  <si>
+    <t>Alabama Department of Mental Health</t>
+  </si>
+  <si>
+    <t>Alabama Department of Senior Services</t>
+  </si>
+  <si>
+    <t>Alabama Board of Medical Examiners</t>
+  </si>
+  <si>
+    <t>Alabama Board of Nursing</t>
+  </si>
+  <si>
+    <t>Alabama State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Alabama Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>Alabama Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Alaska Department of Health</t>
+  </si>
+  <si>
+    <t>Alaska Department of Family and Community Services</t>
+  </si>
+  <si>
+    <t>Alaska Division of Insurance</t>
+  </si>
+  <si>
+    <t>Alaska State Medical Board</t>
+  </si>
+  <si>
+    <t>Alaska Board of Nursing</t>
+  </si>
+  <si>
+    <t>Alaska Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Alaska Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>Alaska Department of Law, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Arizona Department of Health Services</t>
+  </si>
+  <si>
+    <t>Arizona Health Care Cost Containment System (AHCCCS)</t>
+  </si>
+  <si>
+    <t>Arizona Medical Board</t>
+  </si>
+  <si>
+    <t>Arizona Board of Osteopathic Examiners</t>
+  </si>
+  <si>
+    <t>Arizona State Board of Nursing</t>
+  </si>
+  <si>
+    <t>Arizona State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Arizona State Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>Arizona Department of Economic Security</t>
+  </si>
+  <si>
+    <t>Arizona Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Arkansas Department of Health</t>
+  </si>
+  <si>
+    <t>Arkansas Department of Human Services</t>
+  </si>
+  <si>
+    <t>Arkansas Insurance Department</t>
+  </si>
+  <si>
+    <t>Arkansas State Medical Board</t>
+  </si>
+  <si>
+    <t>Arkansas State Board of Nursing</t>
+  </si>
+  <si>
+    <t>Arkansas State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Arkansas State Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>Arkansas Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>California Department of Public Health</t>
+  </si>
+  <si>
+    <t>California Department of Health Care Services</t>
+  </si>
+  <si>
+    <t>California Department of Managed Health Care</t>
+  </si>
+  <si>
+    <t>California Department of Insurance</t>
+  </si>
+  <si>
+    <t>California Department of Social Services</t>
+  </si>
+  <si>
+    <t>California Department of Aging</t>
+  </si>
+  <si>
+    <t>California Department of State Hospitals</t>
+  </si>
+  <si>
+    <t>California Department of Health Care Access and Information (HCAI)</t>
+  </si>
+  <si>
+    <t>Medical Board of California</t>
+  </si>
+  <si>
+    <t>Osteopathic Medical Board of California</t>
+  </si>
+  <si>
+    <t>California Board of Registered Nursing</t>
+  </si>
+  <si>
+    <t>California State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Dental Board of California</t>
+  </si>
+  <si>
+    <t>California Department of Justice, Bureau of Medi-Cal Fraud and Elder Abuse</t>
+  </si>
+  <si>
+    <t>Covered California</t>
+  </si>
+  <si>
+    <t>Colorado Department of Public Health and Environment</t>
+  </si>
+  <si>
+    <t>Colorado Department of Health Care Policy and Financing</t>
+  </si>
+  <si>
+    <t>Colorado Division of Insurance</t>
+  </si>
+  <si>
+    <t>Colorado Behavioral Health Administration</t>
+  </si>
+  <si>
+    <t>Colorado Medical Board</t>
+  </si>
+  <si>
+    <t>Colorado State Board of Nursing</t>
+  </si>
+  <si>
+    <t>Colorado State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Colorado State Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>Colorado Department of Law, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Connect for Health Colorado</t>
+  </si>
+  <si>
+    <t>Connecticut Department of Public Health</t>
+  </si>
+  <si>
+    <t>Connecticut Department of Social Services</t>
+  </si>
+  <si>
+    <t>Connecticut Department of Mental Health and Addiction Services</t>
+  </si>
+  <si>
+    <t>Connecticut Department of Aging and Disability Services</t>
+  </si>
+  <si>
+    <t>Connecticut Medical Examining Board</t>
+  </si>
+  <si>
+    <t>Connecticut Board of Examiners for Nursing</t>
+  </si>
+  <si>
+    <t>Connecticut Commission of Pharmacy</t>
+  </si>
+  <si>
+    <t>Connecticut State Dental Commission</t>
+  </si>
+  <si>
+    <t>Connecticut Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Access Health CT</t>
+  </si>
+  <si>
+    <t>Delaware Division of Public Health</t>
+  </si>
+  <si>
+    <t>Delaware Department of Health and Social Services</t>
+  </si>
+  <si>
+    <t>Delaware Department of Insurance</t>
+  </si>
+  <si>
+    <t>Delaware Division of Substance Abuse and Mental Health</t>
+  </si>
+  <si>
+    <t>Delaware Board of Medical Licensure and Discipline</t>
+  </si>
+  <si>
+    <t>Delaware Board of Nursing</t>
+  </si>
+  <si>
+    <t>Delaware Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Delaware Board of Dentistry and Dental Hygiene</t>
+  </si>
+  <si>
+    <t>Delaware Department of Justice, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>DC Department of Health</t>
+  </si>
+  <si>
+    <t>DC Department of Health Care Finance</t>
+  </si>
+  <si>
+    <t>DC Department of Insurance, Securities and Banking</t>
+  </si>
+  <si>
+    <t>DC Department of Behavioral Health</t>
+  </si>
+  <si>
+    <t>DC Board of Medicine</t>
+  </si>
+  <si>
+    <t>DC Board of Nursing</t>
+  </si>
+  <si>
+    <t>DC Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>DC Board of Dentistry</t>
+  </si>
+  <si>
+    <t>DC Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>DC Health Benefit Exchange Authority</t>
+  </si>
+  <si>
+    <t>Florida Department of Health</t>
+  </si>
+  <si>
+    <t>Florida Agency for Health Care Administration</t>
+  </si>
+  <si>
+    <t>Florida Office of Insurance Regulation</t>
+  </si>
+  <si>
+    <t>Florida Department of Children and Families</t>
+  </si>
+  <si>
+    <t>Florida Department of Elder Affairs</t>
+  </si>
+  <si>
+    <t>Florida Board of Medicine</t>
+  </si>
+  <si>
+    <t>Florida Board of Osteopathic Medicine</t>
+  </si>
+  <si>
+    <t>Florida Board of Nursing</t>
+  </si>
+  <si>
+    <t>Florida Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Florida Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Florida Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Georgia Department of Public Health</t>
+  </si>
+  <si>
+    <t>Georgia Department of Community Health</t>
+  </si>
+  <si>
+    <t>Georgia Department of Behavioral Health and Developmental Disabilities</t>
+  </si>
+  <si>
+    <t>Georgia Department of Human Services</t>
+  </si>
+  <si>
+    <t>Georgia Office of Commissioner of Insurance and Safety Fire</t>
+  </si>
+  <si>
+    <t>Georgia Composite Medical Board</t>
+  </si>
+  <si>
+    <t>Georgia Board of Nursing</t>
+  </si>
+  <si>
+    <t>Georgia State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Georgia Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Georgia Department of Law, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Georgia Access (state-based Marketplace)</t>
+  </si>
+  <si>
+    <t>Hawaii Department of Health</t>
+  </si>
+  <si>
+    <t>Hawaii Department of Human Services, Med-QUEST Division</t>
+  </si>
+  <si>
+    <t>Hawaii Insurance Division (Department of Commerce and Consumer Affairs)</t>
+  </si>
+  <si>
+    <t>Hawaii Medical Board</t>
+  </si>
+  <si>
+    <t>Hawaii Board of Nursing</t>
+  </si>
+  <si>
+    <t>Hawaii Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Hawaii Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>Hawaii Department of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Idaho Department of Health and Welfare</t>
+  </si>
+  <si>
+    <t>Idaho Department of Insurance</t>
+  </si>
+  <si>
+    <t>Idaho State Board of Medicine</t>
+  </si>
+  <si>
+    <t>Idaho Board of Nursing</t>
+  </si>
+  <si>
+    <t>Idaho State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Idaho State Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Idaho Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Your Health Idaho</t>
+  </si>
+  <si>
+    <t>Illinois Department of Public Health</t>
+  </si>
+  <si>
+    <t>Illinois Department of Healthcare and Family Services</t>
+  </si>
+  <si>
+    <t>Illinois Department of Insurance</t>
+  </si>
+  <si>
+    <t>Illinois Department of Human Services</t>
+  </si>
+  <si>
+    <t>Illinois Department on Aging</t>
+  </si>
+  <si>
+    <t>Illinois Office of the Attorney General, Medicaid Fraud Control Bureau</t>
+  </si>
+  <si>
+    <t>Indiana Department of Health</t>
+  </si>
+  <si>
+    <t>Indiana Family and Social Services Administration</t>
+  </si>
+  <si>
+    <t>Indiana Department of Insurance</t>
+  </si>
+  <si>
+    <t>Indiana Medical Licensing Board</t>
+  </si>
+  <si>
+    <t>Indiana State Board of Nursing</t>
+  </si>
+  <si>
+    <t>Indiana Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Indiana State Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Indiana Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Iowa Department of Health and Human Services</t>
+  </si>
+  <si>
+    <t>Iowa Insurance Division</t>
+  </si>
+  <si>
+    <t>Iowa Board of Medicine</t>
+  </si>
+  <si>
+    <t>Iowa Board of Nursing</t>
+  </si>
+  <si>
+    <t>Iowa Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Iowa Dental Board</t>
+  </si>
+  <si>
+    <t>Iowa Department of Inspections, Appeals, and Licensing</t>
+  </si>
+  <si>
+    <t>Iowa Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Kansas Department of Health and Environment</t>
+  </si>
+  <si>
+    <t>Kansas Department for Aging and Disability Services</t>
+  </si>
+  <si>
+    <t>Kansas Department for Children and Families</t>
+  </si>
+  <si>
+    <t>Kansas Insurance Department</t>
+  </si>
+  <si>
+    <t>Kansas State Board of Healing Arts</t>
+  </si>
+  <si>
+    <t>Kansas State Board of Nursing</t>
+  </si>
+  <si>
+    <t>Kansas State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Kansas Dental Board</t>
+  </si>
+  <si>
+    <t>Kansas Office of the Attorney General, Medicaid Fraud and Abuse Division</t>
+  </si>
+  <si>
+    <t>Kentucky Cabinet for Health and Family Services</t>
+  </si>
+  <si>
+    <t>Kentucky Department for Medicaid Services</t>
+  </si>
+  <si>
+    <t>Kentucky Department for Public Health</t>
+  </si>
+  <si>
+    <t>Kentucky Department of Insurance</t>
+  </si>
+  <si>
+    <t>Kentucky Board of Medical Licensure</t>
+  </si>
+  <si>
+    <t>Kentucky Board of Nursing</t>
+  </si>
+  <si>
+    <t>Kentucky Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Kentucky Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Kentucky Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>kynect (state-based Marketplace)</t>
+  </si>
+  <si>
+    <t>Louisiana Department of Health</t>
+  </si>
+  <si>
+    <t>Louisiana Department of Insurance</t>
+  </si>
+  <si>
+    <t>Louisiana State Board of Medical Examiners</t>
+  </si>
+  <si>
+    <t>Louisiana State Board of Nursing</t>
+  </si>
+  <si>
+    <t>Louisiana Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Louisiana State Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Louisiana Department of Justice, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Maine Department of Health and Human Services</t>
+  </si>
+  <si>
+    <t>Maine Center for Disease Control and Prevention</t>
+  </si>
+  <si>
+    <t>Maine Bureau of Insurance</t>
+  </si>
+  <si>
+    <t>Maine Board of Licensure in Medicine</t>
+  </si>
+  <si>
+    <t>Maine Board of Osteopathic Licensure</t>
+  </si>
+  <si>
+    <t>Maine State Board of Nursing</t>
+  </si>
+  <si>
+    <t>Maine Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Maine Board of Dental Practice</t>
+  </si>
+  <si>
+    <t>Maine Office of the Attorney General, Healthcare Crimes Unit</t>
+  </si>
+  <si>
+    <t>CoverME.gov (state-based Marketplace)</t>
+  </si>
+  <si>
+    <t>Maryland Department of Health</t>
+  </si>
+  <si>
+    <t>Maryland Insurance Administration</t>
+  </si>
+  <si>
+    <t>Maryland Department of Aging</t>
+  </si>
+  <si>
+    <t>Maryland Department of Human Services</t>
+  </si>
+  <si>
+    <t>Maryland Board of Physicians</t>
+  </si>
+  <si>
+    <t>Maryland Board of Nursing</t>
+  </si>
+  <si>
+    <t>Maryland Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Maryland State Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>Maryland Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Maryland Health Benefit Exchange</t>
+  </si>
+  <si>
+    <t>Maryland Health Care Commission</t>
+  </si>
+  <si>
+    <t>Maryland Health Services Cost Review Commission</t>
+  </si>
+  <si>
+    <t>Massachusetts Department of Public Health</t>
+  </si>
+  <si>
+    <t>Massachusetts Executive Office of Health and Human Services</t>
+  </si>
+  <si>
+    <t>MassHealth (Medicaid)</t>
+  </si>
+  <si>
+    <t>Massachusetts Division of Insurance</t>
+  </si>
+  <si>
+    <t>Massachusetts Department of Mental Health</t>
+  </si>
+  <si>
+    <t>Massachusetts Executive Office of Elder Affairs</t>
+  </si>
+  <si>
+    <t>Massachusetts Board of Registration in Medicine</t>
+  </si>
+  <si>
+    <t>Massachusetts Board of Registration in Nursing</t>
+  </si>
+  <si>
+    <t>Massachusetts Board of Registration in Pharmacy</t>
+  </si>
+  <si>
+    <t>Massachusetts Board of Registration in Dentistry</t>
+  </si>
+  <si>
+    <t>Massachusetts Office of the Attorney General, Medicaid Fraud Division</t>
+  </si>
+  <si>
+    <t>Massachusetts Health Connector</t>
+  </si>
+  <si>
+    <t>Massachusetts Health Policy Commission</t>
+  </si>
+  <si>
+    <t>Michigan Department of Health and Human Services</t>
+  </si>
+  <si>
+    <t>Michigan Department of Licensing and Regulatory Affairs (LARA)</t>
+  </si>
+  <si>
+    <t>Michigan Board of Medicine</t>
+  </si>
+  <si>
+    <t>Michigan Board of Osteopathic Medicine and Surgery</t>
+  </si>
+  <si>
+    <t>Michigan Board of Nursing</t>
+  </si>
+  <si>
+    <t>Michigan Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Michigan Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Michigan Department of Attorney General, Health Care Fraud Division</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Health</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Human Services</t>
+  </si>
+  <si>
+    <t>Minnesota Board of Medical Practice</t>
+  </si>
+  <si>
+    <t>Minnesota Board of Nursing</t>
+  </si>
+  <si>
+    <t>Minnesota Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Minnesota Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Minnesota Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>MNsure</t>
+  </si>
+  <si>
+    <t>Mississippi State Department of Health</t>
+  </si>
+  <si>
+    <t>Mississippi Division of Medicaid</t>
+  </si>
+  <si>
+    <t>Mississippi Insurance Department</t>
+  </si>
+  <si>
+    <t>Mississippi Department of Mental Health</t>
+  </si>
+  <si>
+    <t>Mississippi State Board of Medical Licensure</t>
+  </si>
+  <si>
+    <t>Mississippi Board of Nursing</t>
+  </si>
+  <si>
+    <t>Mississippi Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Mississippi State Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>Mississippi Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Missouri Department of Health and Senior Services</t>
+  </si>
+  <si>
+    <t>Missouri Department of Social Services, MO HealthNet Division</t>
+  </si>
+  <si>
+    <t>Missouri Department of Mental Health</t>
+  </si>
+  <si>
+    <t>Missouri Department of Commerce and Insurance</t>
+  </si>
+  <si>
+    <t>Missouri State Board of Registration for the Healing Arts</t>
+  </si>
+  <si>
+    <t>Missouri State Board of Nursing</t>
+  </si>
+  <si>
+    <t>Missouri Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Missouri Dental Board</t>
+  </si>
+  <si>
+    <t>Missouri Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Montana Department of Public Health and Human Services</t>
+  </si>
+  <si>
+    <t>Montana Commissioner of Securities and Insurance (State Auditor)</t>
+  </si>
+  <si>
+    <t>Montana Board of Medical Examiners</t>
+  </si>
+  <si>
+    <t>Montana Board of Nursing</t>
+  </si>
+  <si>
+    <t>Montana Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Montana Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Montana Department of Justice, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Nebraska Department of Health and Human Services</t>
+  </si>
+  <si>
+    <t>Nebraska Department of Insurance</t>
+  </si>
+  <si>
+    <t>Nebraska Board of Medicine and Surgery</t>
+  </si>
+  <si>
+    <t>Nebraska Board of Nursing</t>
+  </si>
+  <si>
+    <t>Nebraska Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Nebraska Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Nebraska Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Nevada Department of Health and Human Services</t>
+  </si>
+  <si>
+    <t>Nevada Division of Public and Behavioral Health</t>
+  </si>
+  <si>
+    <t>Nevada Division of Insurance</t>
+  </si>
+  <si>
+    <t>Nevada State Board of Medical Examiners</t>
+  </si>
+  <si>
+    <t>Nevada State Board of Osteopathic Medicine</t>
+  </si>
+  <si>
+    <t>Nevada State Board of Nursing</t>
+  </si>
+  <si>
+    <t>Nevada State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Nevada State Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>Nevada Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Nevada Health Link</t>
+  </si>
+  <si>
+    <t>New Hampshire Department of Health and Human Services</t>
+  </si>
+  <si>
+    <t>New Hampshire Insurance Department</t>
+  </si>
+  <si>
+    <t>New Hampshire Board of Medicine</t>
+  </si>
+  <si>
+    <t>New Hampshire Board of Nursing</t>
+  </si>
+  <si>
+    <t>New Hampshire Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>New Hampshire Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>New Hampshire Department of Justice, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>New Jersey Department of Health</t>
+  </si>
+  <si>
+    <t>New Jersey Department of Human Services</t>
+  </si>
+  <si>
+    <t>New Jersey Division of Medical Assistance and Health Services</t>
+  </si>
+  <si>
+    <t>New Jersey State Board of Medical Examiners</t>
+  </si>
+  <si>
+    <t>New Jersey Board of Nursing</t>
+  </si>
+  <si>
+    <t>New Jersey Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>New Jersey State Board of Dentistry</t>
+  </si>
+  <si>
+    <t>New Jersey Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Get Covered New Jersey</t>
+  </si>
+  <si>
+    <t>New Mexico Department of Health</t>
+  </si>
+  <si>
+    <t>New Mexico Health Care Authority</t>
+  </si>
+  <si>
+    <t>New Mexico Office of Superintendent of Insurance</t>
+  </si>
+  <si>
+    <t>New Mexico Aging and Long-Term Services Department</t>
+  </si>
+  <si>
+    <t>New Mexico Medical Board</t>
+  </si>
+  <si>
+    <t>New Mexico Board of Osteopathic Medical Examiners</t>
+  </si>
+  <si>
+    <t>New Mexico Board of Nursing</t>
+  </si>
+  <si>
+    <t>New Mexico Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>New Mexico Board of Dental Health Care</t>
+  </si>
+  <si>
+    <t>New Mexico Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>BeWellnm (state-based Marketplace)</t>
+  </si>
+  <si>
+    <t>New York State Department of Health</t>
+  </si>
+  <si>
+    <t>New York State Office of Mental Health</t>
+  </si>
+  <si>
+    <t>New York State Office of Addiction Services and Supports (OASAS)</t>
+  </si>
+  <si>
+    <t>New York State Office for the Aging</t>
+  </si>
+  <si>
+    <t>New York State Education Department, Office of the Professions</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>NY State of Health (state-based Marketplace)</t>
+  </si>
+  <si>
+    <t>North Carolina Department of Health and Human Services</t>
+  </si>
+  <si>
+    <t>North Carolina Department of Insurance</t>
+  </si>
+  <si>
+    <t>North Carolina Medical Board</t>
+  </si>
+  <si>
+    <t>North Carolina Board of Nursing</t>
+  </si>
+  <si>
+    <t>North Carolina Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>North Carolina State Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>North Carolina Department of Justice, Medicaid Investigations Division</t>
+  </si>
+  <si>
+    <t>North Dakota Department of Health and Human Services</t>
+  </si>
+  <si>
+    <t>North Dakota Insurance Department</t>
+  </si>
+  <si>
+    <t>North Dakota Board of Medicine</t>
+  </si>
+  <si>
+    <t>North Dakota Board of Nursing</t>
+  </si>
+  <si>
+    <t>North Dakota State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>North Dakota State Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>North Dakota Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Ohio Department of Health</t>
+  </si>
+  <si>
+    <t>Ohio Department of Medicaid</t>
+  </si>
+  <si>
+    <t>Ohio Department of Mental Health and Addiction Services</t>
+  </si>
+  <si>
+    <t>Ohio Department of Aging</t>
+  </si>
+  <si>
+    <t>Ohio Department of Insurance</t>
+  </si>
+  <si>
+    <t>State Medical Board of Ohio</t>
+  </si>
+  <si>
+    <t>Ohio Board of Nursing</t>
+  </si>
+  <si>
+    <t>State of Ohio Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Ohio State Dental Board</t>
+  </si>
+  <si>
+    <t>Ohio Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Oklahoma State Department of Health</t>
+  </si>
+  <si>
+    <t>Oklahoma Health Care Authority</t>
+  </si>
+  <si>
+    <t>Oklahoma Insurance Department</t>
+  </si>
+  <si>
+    <t>Oklahoma Department of Mental Health and Substance Abuse Services</t>
+  </si>
+  <si>
+    <t>Oklahoma State Board of Medical Licensure and Supervision</t>
+  </si>
+  <si>
+    <t>Oklahoma State Board of Osteopathic Examiners</t>
+  </si>
+  <si>
+    <t>Oklahoma Board of Nursing</t>
+  </si>
+  <si>
+    <t>Oklahoma State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Oklahoma Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Oklahoma Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Oregon Health Authority</t>
+  </si>
+  <si>
+    <t>Oregon Department of Human Services</t>
+  </si>
+  <si>
+    <t>Oregon Department of Consumer and Business Services, Division of Financial Regulation</t>
+  </si>
+  <si>
+    <t>Oregon Medical Board</t>
+  </si>
+  <si>
+    <t>Oregon State Board of Nursing</t>
+  </si>
+  <si>
+    <t>Oregon Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Oregon Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Oregon Department of Justice, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Pennsylvania Department of Health</t>
+  </si>
+  <si>
+    <t>Pennsylvania Department of Human Services</t>
+  </si>
+  <si>
+    <t>Pennsylvania Insurance Department</t>
+  </si>
+  <si>
+    <t>Pennsylvania Department of Aging</t>
+  </si>
+  <si>
+    <t>Pennsylvania Department of Drug and Alcohol Programs</t>
+  </si>
+  <si>
+    <t>Pennsylvania State Board of Medicine</t>
+  </si>
+  <si>
+    <t>Pennsylvania State Board of Osteopathic Medicine</t>
+  </si>
+  <si>
+    <t>Pennsylvania State Board of Nursing</t>
+  </si>
+  <si>
+    <t>Pennsylvania State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Pennsylvania State Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Pennsylvania Office of the Attorney General, Medicaid Fraud Control Section</t>
+  </si>
+  <si>
+    <t>Pennie (state-based Marketplace)</t>
+  </si>
+  <si>
+    <t>Rhode Island Department of Health</t>
+  </si>
+  <si>
+    <t>Rhode Island Executive Office of Health and Human Services</t>
+  </si>
+  <si>
+    <t>Rhode Island Department of Behavioral Healthcare, Developmental Disabilities and Hospitals</t>
+  </si>
+  <si>
+    <t>Rhode Island Department of Business Regulation, Insurance Division</t>
+  </si>
+  <si>
+    <t>Rhode Island Office of the Health Insurance Commissioner</t>
+  </si>
+  <si>
+    <t>Rhode Island Board of Medical Licensure and Discipline</t>
+  </si>
+  <si>
+    <t>Rhode Island Board of Nurse Registration and Nursing Education</t>
+  </si>
+  <si>
+    <t>Rhode Island Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Rhode Island Board of Examiners in Dentistry</t>
+  </si>
+  <si>
+    <t>Rhode Island Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>HealthSource RI</t>
+  </si>
+  <si>
+    <t>South Carolina Department of Public Health</t>
+  </si>
+  <si>
+    <t>South Carolina Department of Health and Human Services</t>
+  </si>
+  <si>
+    <t>South Carolina Department of Mental Health</t>
+  </si>
+  <si>
+    <t>South Carolina Department on Aging</t>
+  </si>
+  <si>
+    <t>South Carolina Department of Insurance</t>
+  </si>
+  <si>
+    <t>South Carolina Board of Medical Examiners</t>
+  </si>
+  <si>
+    <t>South Carolina State Board of Nursing</t>
+  </si>
+  <si>
+    <t>South Carolina Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>South Carolina Board of Dentistry</t>
+  </si>
+  <si>
+    <t>South Carolina Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>South Dakota Department of Health</t>
+  </si>
+  <si>
+    <t>South Dakota Department of Social Services</t>
+  </si>
+  <si>
+    <t>South Dakota Division of Insurance</t>
+  </si>
+  <si>
+    <t>South Dakota State Board of Medical and Osteopathic Examiners</t>
+  </si>
+  <si>
+    <t>South Dakota Board of Nursing</t>
+  </si>
+  <si>
+    <t>South Dakota Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>South Dakota State Board of Dentistry</t>
+  </si>
+  <si>
+    <t>South Dakota Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Tennessee Department of Health</t>
+  </si>
+  <si>
+    <t>Tennessee Department of Mental Health and Substance Abuse Services</t>
+  </si>
+  <si>
+    <t>TennCare (Bureau of TennCare)</t>
+  </si>
+  <si>
+    <t>Tennessee Department of Commerce and Insurance</t>
+  </si>
+  <si>
+    <t>Tennessee Department of Disability and Aging</t>
+  </si>
+  <si>
+    <t>Tennessee Board of Medical Examiners</t>
+  </si>
+  <si>
+    <t>Tennessee Board of Osteopathic Examination</t>
+  </si>
+  <si>
+    <t>Tennessee Board of Nursing</t>
+  </si>
+  <si>
+    <t>Tennessee Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Tennessee Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Tennessee Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Texas Department of State Health Services</t>
+  </si>
+  <si>
+    <t>Texas Health and Human Services Commission</t>
+  </si>
+  <si>
+    <t>Texas Department of Insurance</t>
+  </si>
+  <si>
+    <t>Texas Medical Board</t>
+  </si>
+  <si>
+    <t>Texas Board of Nursing</t>
+  </si>
+  <si>
+    <t>Texas State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Texas State Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>Texas Office of the Attorney General, Civil Medicaid Fraud Division</t>
+  </si>
+  <si>
+    <t>Utah Department of Health and Human Services</t>
+  </si>
+  <si>
+    <t>Utah Insurance Department</t>
+  </si>
+  <si>
+    <t>Utah Division of Professional Licensing</t>
+  </si>
+  <si>
+    <t>Utah Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Vermont Department of Health</t>
+  </si>
+  <si>
+    <t>Vermont Agency of Human Services</t>
+  </si>
+  <si>
+    <t>Vermont Department of Vermont Health Access</t>
+  </si>
+  <si>
+    <t>Vermont Department of Mental Health</t>
+  </si>
+  <si>
+    <t>Vermont Department of Disabilities, Aging and Independent Living</t>
+  </si>
+  <si>
+    <t>Vermont Green Mountain Care Board</t>
+  </si>
+  <si>
+    <t>Vermont Board of Medical Practice</t>
+  </si>
+  <si>
+    <t>Vermont State Board of Nursing</t>
+  </si>
+  <si>
+    <t>Vermont Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Vermont Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>Vermont Office of the Attorney General, Medicaid Fraud and Residential Abuse Unit</t>
+  </si>
+  <si>
+    <t>Vermont Health Connect</t>
+  </si>
+  <si>
+    <t>Virginia Department of Health</t>
+  </si>
+  <si>
+    <t>Virginia Department of Medical Assistance Services</t>
+  </si>
+  <si>
+    <t>Virginia Department of Behavioral Health and Developmental Services</t>
+  </si>
+  <si>
+    <t>Virginia Bureau of Insurance (State Corporation Commission)</t>
+  </si>
+  <si>
+    <t>Virginia Board of Medicine</t>
+  </si>
+  <si>
+    <t>Virginia Board of Nursing</t>
+  </si>
+  <si>
+    <t>Virginia Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Virginia Board of Dentistry</t>
+  </si>
+  <si>
+    <t>Virginia Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Virginia's Insurance Marketplace</t>
+  </si>
+  <si>
+    <t>Washington State Department of Health</t>
+  </si>
+  <si>
+    <t>Washington State Health Care Authority</t>
+  </si>
+  <si>
+    <t>Washington State Department of Social and Health Services</t>
+  </si>
+  <si>
+    <t>Washington State Office of the Insurance Commissioner</t>
+  </si>
+  <si>
+    <t>Washington Medical Commission</t>
+  </si>
+  <si>
+    <t>Washington State Board of Osteopathic Medicine and Surgery</t>
+  </si>
+  <si>
+    <t>Washington State Nursing Care Quality Assurance Commission</t>
+  </si>
+  <si>
+    <t>Washington State Pharmacy Quality Assurance Commission</t>
+  </si>
+  <si>
+    <t>Washington State Dental Quality Assurance Commission</t>
+  </si>
+  <si>
+    <t>Washington State Office of the Attorney General, Medicaid Fraud Control Division</t>
+  </si>
+  <si>
+    <t>Washington Health Benefit Exchange</t>
+  </si>
+  <si>
+    <t>West Virginia Department of Health</t>
+  </si>
+  <si>
+    <t>West Virginia Department of Health Facilities</t>
+  </si>
+  <si>
+    <t>West Virginia Department of Human Services</t>
+  </si>
+  <si>
+    <t>West Virginia Offices of the Insurance Commissioner</t>
+  </si>
+  <si>
+    <t>West Virginia Board of Medicine</t>
+  </si>
+  <si>
+    <t>West Virginia Board of Osteopathic Medicine</t>
+  </si>
+  <si>
+    <t>West Virginia Board of Examiners for Registered Professional Nurses</t>
+  </si>
+  <si>
+    <t>West Virginia Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>West Virginia Board of Dentistry</t>
+  </si>
+  <si>
+    <t>West Virginia Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Wisconsin Department of Health Services</t>
+  </si>
+  <si>
+    <t>Wisconsin Office of the Commissioner of Insurance</t>
+  </si>
+  <si>
+    <t>Wisconsin Department of Safety and Professional Services</t>
+  </si>
+  <si>
+    <t>Wisconsin Medical Examining Board</t>
+  </si>
+  <si>
+    <t>Wisconsin Board of Nursing</t>
+  </si>
+  <si>
+    <t>Wisconsin Pharmacy Examining Board</t>
+  </si>
+  <si>
+    <t>Wisconsin Dentistry Examining Board</t>
+  </si>
+  <si>
+    <t>Wisconsin Department of Justice, Medicaid Fraud Control and Elder Abuse Unit</t>
+  </si>
+  <si>
+    <t>Wyoming Department of Health</t>
+  </si>
+  <si>
+    <t>Wyoming Department of Insurance</t>
+  </si>
+  <si>
+    <t>Wyoming Board of Medicine</t>
+  </si>
+  <si>
+    <t>Wyoming State Board of Nursing</t>
+  </si>
+  <si>
+    <t>Wyoming State Board of Pharmacy</t>
+  </si>
+  <si>
+    <t>Wyoming Board of Dental Examiners</t>
+  </si>
+  <si>
+    <t>Wyoming Office of the Attorney General, Medicaid Fraud Control Unit</t>
+  </si>
+  <si>
+    <t>Puerto Rico Department of Health</t>
+  </si>
+  <si>
+    <t>Puerto Rico Health Insurance Administration (ASES)</t>
+  </si>
+  <si>
+    <t>Puerto Rico Office of the Insurance Commissioner</t>
+  </si>
+  <si>
+    <t>Puerto Rico Board of Medical Licensure and Discipline</t>
+  </si>
+  <si>
+    <t>U.S. Virgin Islands Department of Health</t>
+  </si>
+  <si>
+    <t>U.S. Virgin Islands Department of Human Services</t>
+  </si>
+  <si>
+    <t>U.S. Virgin Islands Division of Banking, Insurance and Financial Regulation</t>
+  </si>
+  <si>
+    <t>Guam Department of Public Health and Social Services</t>
+  </si>
+  <si>
+    <t>Guam Department of Revenue and Taxation, Insurance Branch</t>
+  </si>
+  <si>
+    <t>American Samoa Department of Health</t>
+  </si>
+  <si>
+    <t>American Samoa Office of the Governor, Office of Insurance Commissioner</t>
+  </si>
+  <si>
+    <t>CNMI Commonwealth Healthcare Corporation</t>
+  </si>
+  <si>
+    <t>CNMI Department of Commerce, Insurance Division</t>
   </si>
 </sst>
 </file>
@@ -3407,7 +4994,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3456,6 +5043,10 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -3487,7 +5078,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3510,11 +5101,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD4D4D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD4D4D4"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3547,7 +5149,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="8" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3882,7 +5491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C767"/>
+  <dimension ref="A1:C1304"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
@@ -12324,6 +13933,5913 @@
       </c>
       <c r="C767" s="4" t="s">
         <v>877</v>
+      </c>
+    </row>
+    <row r="768" spans="1:3" ht="17">
+      <c r="A768" t="s">
+        <v>28</v>
+      </c>
+      <c r="B768" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C768" s="3" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="769" spans="1:3" ht="17">
+      <c r="A769" t="s">
+        <v>28</v>
+      </c>
+      <c r="B769" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C769" s="16" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="770" spans="1:3" ht="17">
+      <c r="A770" t="s">
+        <v>28</v>
+      </c>
+      <c r="B770" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C770" s="17" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" ht="17">
+      <c r="A771" t="s">
+        <v>28</v>
+      </c>
+      <c r="B771" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C771" s="3" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" ht="17">
+      <c r="A772" t="s">
+        <v>3</v>
+      </c>
+      <c r="B772" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C772" s="19" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" ht="17">
+      <c r="A773" t="s">
+        <v>3</v>
+      </c>
+      <c r="B773" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C773" s="19" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="774" spans="1:3" ht="17">
+      <c r="A774" t="s">
+        <v>3</v>
+      </c>
+      <c r="B774" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C774" s="19" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3" ht="17">
+      <c r="A775" t="s">
+        <v>3</v>
+      </c>
+      <c r="B775" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C775" s="19" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" ht="17">
+      <c r="A776" t="s">
+        <v>3</v>
+      </c>
+      <c r="B776" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C776" s="19" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" ht="17">
+      <c r="A777" t="s">
+        <v>3</v>
+      </c>
+      <c r="B777" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C777" s="19" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="778" spans="1:3" ht="17">
+      <c r="A778" t="s">
+        <v>3</v>
+      </c>
+      <c r="B778" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C778" s="19" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" ht="17">
+      <c r="A779" t="s">
+        <v>3</v>
+      </c>
+      <c r="B779" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C779" s="19" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" ht="17">
+      <c r="A780" t="s">
+        <v>3</v>
+      </c>
+      <c r="B780" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C780" s="19" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3" ht="17">
+      <c r="A781" t="s">
+        <v>3</v>
+      </c>
+      <c r="B781" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C781" s="19" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3" ht="17">
+      <c r="A782" t="s">
+        <v>3</v>
+      </c>
+      <c r="B782" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C782" s="19" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="783" spans="1:3" ht="17">
+      <c r="A783" t="s">
+        <v>3</v>
+      </c>
+      <c r="B783" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C783" s="19" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="784" spans="1:3" ht="17">
+      <c r="A784" t="s">
+        <v>3</v>
+      </c>
+      <c r="B784" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C784" s="19" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="785" spans="1:3" ht="17">
+      <c r="A785" t="s">
+        <v>3</v>
+      </c>
+      <c r="B785" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C785" s="19" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="786" spans="1:3" ht="17">
+      <c r="A786" t="s">
+        <v>3</v>
+      </c>
+      <c r="B786" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C786" s="19" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="787" spans="1:3" ht="17">
+      <c r="A787" t="s">
+        <v>3</v>
+      </c>
+      <c r="B787" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C787" s="19" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="788" spans="1:3" ht="17">
+      <c r="A788" t="s">
+        <v>3</v>
+      </c>
+      <c r="B788" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C788" s="19" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="789" spans="1:3" ht="17">
+      <c r="A789" t="s">
+        <v>3</v>
+      </c>
+      <c r="B789" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C789" s="19" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="790" spans="1:3" ht="17">
+      <c r="A790" t="s">
+        <v>3</v>
+      </c>
+      <c r="B790" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C790" s="19" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" ht="17">
+      <c r="A791" t="s">
+        <v>3</v>
+      </c>
+      <c r="B791" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C791" s="19" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="792" spans="1:3" ht="17">
+      <c r="A792" t="s">
+        <v>3</v>
+      </c>
+      <c r="B792" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C792" s="19" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="793" spans="1:3" ht="17">
+      <c r="A793" t="s">
+        <v>3</v>
+      </c>
+      <c r="B793" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C793" s="19" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" ht="17">
+      <c r="A794" t="s">
+        <v>3</v>
+      </c>
+      <c r="B794" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C794" s="19" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" ht="17">
+      <c r="A795" t="s">
+        <v>3</v>
+      </c>
+      <c r="B795" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C795" s="19" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" ht="17">
+      <c r="A796" t="s">
+        <v>3</v>
+      </c>
+      <c r="B796" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C796" s="19" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" ht="17">
+      <c r="A797" t="s">
+        <v>3</v>
+      </c>
+      <c r="B797" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C797" s="19" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3" ht="17">
+      <c r="A798" t="s">
+        <v>3</v>
+      </c>
+      <c r="B798" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C798" s="19" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="799" spans="1:3" ht="17">
+      <c r="A799" t="s">
+        <v>3</v>
+      </c>
+      <c r="B799" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C799" s="19" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" ht="17">
+      <c r="A800" t="s">
+        <v>3</v>
+      </c>
+      <c r="B800" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C800" s="19" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="801" spans="1:3" ht="17">
+      <c r="A801" t="s">
+        <v>3</v>
+      </c>
+      <c r="B801" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C801" s="19" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="802" spans="1:3" ht="17">
+      <c r="A802" t="s">
+        <v>3</v>
+      </c>
+      <c r="B802" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C802" s="19" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3" ht="17">
+      <c r="A803" t="s">
+        <v>3</v>
+      </c>
+      <c r="B803" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C803" s="19" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="804" spans="1:3" ht="17">
+      <c r="A804" t="s">
+        <v>3</v>
+      </c>
+      <c r="B804" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C804" s="19" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="805" spans="1:3" ht="17">
+      <c r="A805" t="s">
+        <v>3</v>
+      </c>
+      <c r="B805" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C805" s="19" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" ht="17">
+      <c r="A806" t="s">
+        <v>3</v>
+      </c>
+      <c r="B806" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C806" s="19" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="807" spans="1:3" ht="17">
+      <c r="A807" t="s">
+        <v>3</v>
+      </c>
+      <c r="B807" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C807" s="19" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="808" spans="1:3" ht="17">
+      <c r="A808" t="s">
+        <v>3</v>
+      </c>
+      <c r="B808" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C808" s="19" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="809" spans="1:3" ht="17">
+      <c r="A809" t="s">
+        <v>3</v>
+      </c>
+      <c r="B809" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C809" s="19" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="810" spans="1:3" ht="17">
+      <c r="A810" t="s">
+        <v>3</v>
+      </c>
+      <c r="B810" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C810" s="19" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="811" spans="1:3" ht="17">
+      <c r="A811" t="s">
+        <v>3</v>
+      </c>
+      <c r="B811" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C811" s="19" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3" ht="17">
+      <c r="A812" t="s">
+        <v>3</v>
+      </c>
+      <c r="B812" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C812" s="19" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="813" spans="1:3" ht="17">
+      <c r="A813" t="s">
+        <v>3</v>
+      </c>
+      <c r="B813" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C813" s="19" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="814" spans="1:3" ht="17">
+      <c r="A814" t="s">
+        <v>3</v>
+      </c>
+      <c r="B814" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C814" s="19" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="815" spans="1:3" ht="17">
+      <c r="A815" t="s">
+        <v>3</v>
+      </c>
+      <c r="B815" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C815" s="19" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="816" spans="1:3" ht="17">
+      <c r="A816" t="s">
+        <v>3</v>
+      </c>
+      <c r="B816" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C816" s="19" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="817" spans="1:3" ht="17">
+      <c r="A817" t="s">
+        <v>3</v>
+      </c>
+      <c r="B817" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C817" s="19" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="818" spans="1:3" ht="17">
+      <c r="A818" t="s">
+        <v>3</v>
+      </c>
+      <c r="B818" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C818" s="19" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="819" spans="1:3" ht="17">
+      <c r="A819" t="s">
+        <v>3</v>
+      </c>
+      <c r="B819" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C819" s="19" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="820" spans="1:3" ht="17">
+      <c r="A820" t="s">
+        <v>3</v>
+      </c>
+      <c r="B820" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C820" s="19" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="821" spans="1:3" ht="17">
+      <c r="A821" t="s">
+        <v>3</v>
+      </c>
+      <c r="B821" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C821" s="19" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="822" spans="1:3" ht="17">
+      <c r="A822" t="s">
+        <v>3</v>
+      </c>
+      <c r="B822" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C822" s="19" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="823" spans="1:3" ht="17">
+      <c r="A823" t="s">
+        <v>3</v>
+      </c>
+      <c r="B823" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C823" s="19" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="824" spans="1:3" ht="17">
+      <c r="A824" t="s">
+        <v>3</v>
+      </c>
+      <c r="B824" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C824" s="19" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="825" spans="1:3" ht="17">
+      <c r="A825" t="s">
+        <v>3</v>
+      </c>
+      <c r="B825" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C825" s="19" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="826" spans="1:3" ht="17">
+      <c r="A826" t="s">
+        <v>3</v>
+      </c>
+      <c r="B826" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C826" s="19" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3" ht="17">
+      <c r="A827" t="s">
+        <v>3</v>
+      </c>
+      <c r="B827" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C827" s="19" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="828" spans="1:3" ht="17">
+      <c r="A828" t="s">
+        <v>3</v>
+      </c>
+      <c r="B828" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C828" s="19" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="829" spans="1:3" ht="17">
+      <c r="A829" t="s">
+        <v>3</v>
+      </c>
+      <c r="B829" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C829" s="19" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3" ht="17">
+      <c r="A830" t="s">
+        <v>3</v>
+      </c>
+      <c r="B830" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C830" s="19" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="831" spans="1:3" ht="17">
+      <c r="A831" t="s">
+        <v>3</v>
+      </c>
+      <c r="B831" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C831" s="19" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="832" spans="1:3" ht="17">
+      <c r="A832" t="s">
+        <v>3</v>
+      </c>
+      <c r="B832" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C832" s="19" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="833" spans="1:3" ht="17">
+      <c r="A833" t="s">
+        <v>3</v>
+      </c>
+      <c r="B833" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C833" s="19" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="834" spans="1:3" ht="17">
+      <c r="A834" t="s">
+        <v>3</v>
+      </c>
+      <c r="B834" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C834" s="19" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="835" spans="1:3" ht="17">
+      <c r="A835" t="s">
+        <v>3</v>
+      </c>
+      <c r="B835" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C835" s="19" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3" ht="17">
+      <c r="A836" t="s">
+        <v>3</v>
+      </c>
+      <c r="B836" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C836" s="19" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="837" spans="1:3" ht="17">
+      <c r="A837" t="s">
+        <v>3</v>
+      </c>
+      <c r="B837" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C837" s="19" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="838" spans="1:3" ht="17">
+      <c r="A838" t="s">
+        <v>3</v>
+      </c>
+      <c r="B838" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C838" s="19" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="839" spans="1:3" ht="17">
+      <c r="A839" t="s">
+        <v>3</v>
+      </c>
+      <c r="B839" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C839" s="19" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="840" spans="1:3" ht="17">
+      <c r="A840" t="s">
+        <v>3</v>
+      </c>
+      <c r="B840" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C840" s="19" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3" ht="17">
+      <c r="A841" t="s">
+        <v>3</v>
+      </c>
+      <c r="B841" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C841" s="19" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="842" spans="1:3" ht="17">
+      <c r="A842" t="s">
+        <v>3</v>
+      </c>
+      <c r="B842" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C842" s="19" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="843" spans="1:3" ht="17">
+      <c r="A843" t="s">
+        <v>3</v>
+      </c>
+      <c r="B843" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C843" s="19" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="844" spans="1:3" ht="17">
+      <c r="A844" t="s">
+        <v>3</v>
+      </c>
+      <c r="B844" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C844" s="19" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="845" spans="1:3" ht="17">
+      <c r="A845" t="s">
+        <v>3</v>
+      </c>
+      <c r="B845" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C845" s="19" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="846" spans="1:3" ht="17">
+      <c r="A846" t="s">
+        <v>3</v>
+      </c>
+      <c r="B846" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C846" s="19" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="847" spans="1:3" ht="17">
+      <c r="A847" t="s">
+        <v>3</v>
+      </c>
+      <c r="B847" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C847" s="19" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="848" spans="1:3" ht="17">
+      <c r="A848" t="s">
+        <v>3</v>
+      </c>
+      <c r="B848" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C848" s="19" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="849" spans="1:3" ht="17">
+      <c r="A849" t="s">
+        <v>3</v>
+      </c>
+      <c r="B849" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C849" s="19" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="850" spans="1:3" ht="17">
+      <c r="A850" t="s">
+        <v>3</v>
+      </c>
+      <c r="B850" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C850" s="19" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="851" spans="1:3" ht="17">
+      <c r="A851" t="s">
+        <v>3</v>
+      </c>
+      <c r="B851" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C851" s="19" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="852" spans="1:3" ht="17">
+      <c r="A852" t="s">
+        <v>3</v>
+      </c>
+      <c r="B852" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C852" s="19" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="853" spans="1:3" ht="17">
+      <c r="A853" t="s">
+        <v>3</v>
+      </c>
+      <c r="B853" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C853" s="19" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3" ht="17">
+      <c r="A854" t="s">
+        <v>3</v>
+      </c>
+      <c r="B854" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C854" s="19" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="855" spans="1:3" ht="17">
+      <c r="A855" t="s">
+        <v>3</v>
+      </c>
+      <c r="B855" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C855" s="19" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="856" spans="1:3" ht="17">
+      <c r="A856" t="s">
+        <v>3</v>
+      </c>
+      <c r="B856" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C856" s="19" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="857" spans="1:3" ht="17">
+      <c r="A857" t="s">
+        <v>3</v>
+      </c>
+      <c r="B857" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C857" s="19" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="858" spans="1:3" ht="17">
+      <c r="A858" t="s">
+        <v>3</v>
+      </c>
+      <c r="B858" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C858" s="19" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="859" spans="1:3" ht="17">
+      <c r="A859" t="s">
+        <v>3</v>
+      </c>
+      <c r="B859" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C859" s="19" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3" ht="17">
+      <c r="A860" t="s">
+        <v>3</v>
+      </c>
+      <c r="B860" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C860" s="19" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3" ht="17">
+      <c r="A861" t="s">
+        <v>3</v>
+      </c>
+      <c r="B861" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C861" s="19" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3" ht="17">
+      <c r="A862" t="s">
+        <v>3</v>
+      </c>
+      <c r="B862" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C862" s="19" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" ht="17">
+      <c r="A863" t="s">
+        <v>3</v>
+      </c>
+      <c r="B863" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C863" s="19" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" ht="17">
+      <c r="A864" t="s">
+        <v>3</v>
+      </c>
+      <c r="B864" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C864" s="19" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" ht="17">
+      <c r="A865" t="s">
+        <v>3</v>
+      </c>
+      <c r="B865" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C865" s="19" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" ht="17">
+      <c r="A866" t="s">
+        <v>3</v>
+      </c>
+      <c r="B866" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C866" s="19" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" ht="17">
+      <c r="A867" t="s">
+        <v>3</v>
+      </c>
+      <c r="B867" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C867" s="19" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" ht="17">
+      <c r="A868" t="s">
+        <v>3</v>
+      </c>
+      <c r="B868" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C868" s="19" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" ht="17">
+      <c r="A869" t="s">
+        <v>3</v>
+      </c>
+      <c r="B869" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C869" s="19" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" ht="17">
+      <c r="A870" t="s">
+        <v>3</v>
+      </c>
+      <c r="B870" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C870" s="19" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" ht="17">
+      <c r="A871" t="s">
+        <v>3</v>
+      </c>
+      <c r="B871" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C871" s="19" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" ht="17">
+      <c r="A872" t="s">
+        <v>3</v>
+      </c>
+      <c r="B872" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C872" s="19" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" ht="17">
+      <c r="A873" t="s">
+        <v>3</v>
+      </c>
+      <c r="B873" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C873" s="19" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" ht="17">
+      <c r="A874" t="s">
+        <v>3</v>
+      </c>
+      <c r="B874" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C874" s="19" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" ht="17">
+      <c r="A875" t="s">
+        <v>3</v>
+      </c>
+      <c r="B875" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C875" s="19" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" ht="17">
+      <c r="A876" t="s">
+        <v>3</v>
+      </c>
+      <c r="B876" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C876" s="19" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" ht="17">
+      <c r="A877" t="s">
+        <v>3</v>
+      </c>
+      <c r="B877" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C877" s="19" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" ht="17">
+      <c r="A878" t="s">
+        <v>3</v>
+      </c>
+      <c r="B878" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C878" s="19" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" ht="17">
+      <c r="A879" t="s">
+        <v>3</v>
+      </c>
+      <c r="B879" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C879" s="19" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" ht="17">
+      <c r="A880" t="s">
+        <v>3</v>
+      </c>
+      <c r="B880" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C880" s="19" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" ht="17">
+      <c r="A881" t="s">
+        <v>3</v>
+      </c>
+      <c r="B881" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C881" s="19" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" ht="17">
+      <c r="A882" t="s">
+        <v>3</v>
+      </c>
+      <c r="B882" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C882" s="19" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="883" spans="1:3" ht="17">
+      <c r="A883" t="s">
+        <v>3</v>
+      </c>
+      <c r="B883" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C883" s="19" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" ht="17">
+      <c r="A884" t="s">
+        <v>3</v>
+      </c>
+      <c r="B884" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C884" s="19" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="885" spans="1:3" ht="17">
+      <c r="A885" t="s">
+        <v>3</v>
+      </c>
+      <c r="B885" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C885" s="19" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="886" spans="1:3" ht="17">
+      <c r="A886" t="s">
+        <v>3</v>
+      </c>
+      <c r="B886" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C886" s="19" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" ht="17">
+      <c r="A887" t="s">
+        <v>3</v>
+      </c>
+      <c r="B887" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C887" s="19" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="888" spans="1:3" ht="17">
+      <c r="A888" t="s">
+        <v>3</v>
+      </c>
+      <c r="B888" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C888" s="19" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="889" spans="1:3" ht="17">
+      <c r="A889" t="s">
+        <v>3</v>
+      </c>
+      <c r="B889" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C889" s="19" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="890" spans="1:3" ht="17">
+      <c r="A890" t="s">
+        <v>3</v>
+      </c>
+      <c r="B890" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C890" s="19" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="891" spans="1:3" ht="17">
+      <c r="A891" t="s">
+        <v>3</v>
+      </c>
+      <c r="B891" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C891" s="19" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="892" spans="1:3" ht="17">
+      <c r="A892" t="s">
+        <v>3</v>
+      </c>
+      <c r="B892" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C892" s="19" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="893" spans="1:3" ht="17">
+      <c r="A893" t="s">
+        <v>3</v>
+      </c>
+      <c r="B893" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C893" s="19" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="894" spans="1:3" ht="17">
+      <c r="A894" t="s">
+        <v>3</v>
+      </c>
+      <c r="B894" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C894" s="19" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="895" spans="1:3" ht="17">
+      <c r="A895" t="s">
+        <v>3</v>
+      </c>
+      <c r="B895" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C895" s="19" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="896" spans="1:3" ht="17">
+      <c r="A896" t="s">
+        <v>3</v>
+      </c>
+      <c r="B896" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C896" s="19" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="897" spans="1:3" ht="17">
+      <c r="A897" t="s">
+        <v>3</v>
+      </c>
+      <c r="B897" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C897" s="19" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3" ht="17">
+      <c r="A898" t="s">
+        <v>3</v>
+      </c>
+      <c r="B898" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C898" s="19" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" ht="17">
+      <c r="A899" t="s">
+        <v>3</v>
+      </c>
+      <c r="B899" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C899" s="19" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="900" spans="1:3" ht="17">
+      <c r="A900" t="s">
+        <v>3</v>
+      </c>
+      <c r="B900" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C900" s="19" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="901" spans="1:3" ht="17">
+      <c r="A901" t="s">
+        <v>3</v>
+      </c>
+      <c r="B901" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C901" s="19" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="902" spans="1:3" ht="17">
+      <c r="A902" t="s">
+        <v>3</v>
+      </c>
+      <c r="B902" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C902" s="19" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="903" spans="1:3" ht="17">
+      <c r="A903" t="s">
+        <v>3</v>
+      </c>
+      <c r="B903" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C903" s="19" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="904" spans="1:3" ht="17">
+      <c r="A904" t="s">
+        <v>3</v>
+      </c>
+      <c r="B904" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C904" s="19" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3" ht="17">
+      <c r="A905" t="s">
+        <v>3</v>
+      </c>
+      <c r="B905" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C905" s="19" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3" ht="17">
+      <c r="A906" t="s">
+        <v>3</v>
+      </c>
+      <c r="B906" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C906" s="19" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="907" spans="1:3" ht="17">
+      <c r="A907" t="s">
+        <v>3</v>
+      </c>
+      <c r="B907" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C907" s="19" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3" ht="17">
+      <c r="A908" t="s">
+        <v>3</v>
+      </c>
+      <c r="B908" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C908" s="19" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3" ht="17">
+      <c r="A909" t="s">
+        <v>3</v>
+      </c>
+      <c r="B909" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C909" s="19" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3" ht="17">
+      <c r="A910" t="s">
+        <v>3</v>
+      </c>
+      <c r="B910" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C910" s="19" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3" ht="17">
+      <c r="A911" t="s">
+        <v>3</v>
+      </c>
+      <c r="B911" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C911" s="19" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3" ht="17">
+      <c r="A912" t="s">
+        <v>3</v>
+      </c>
+      <c r="B912" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C912" s="19" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="913" spans="1:3" ht="17">
+      <c r="A913" t="s">
+        <v>3</v>
+      </c>
+      <c r="B913" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C913" s="19" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3" ht="17">
+      <c r="A914" t="s">
+        <v>3</v>
+      </c>
+      <c r="B914" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C914" s="19" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3" ht="17">
+      <c r="A915" t="s">
+        <v>3</v>
+      </c>
+      <c r="B915" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C915" s="19" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3" ht="17">
+      <c r="A916" t="s">
+        <v>3</v>
+      </c>
+      <c r="B916" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C916" s="19" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3" ht="17">
+      <c r="A917" t="s">
+        <v>3</v>
+      </c>
+      <c r="B917" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C917" s="19" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3" ht="17">
+      <c r="A918" t="s">
+        <v>3</v>
+      </c>
+      <c r="B918" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C918" s="19" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3" ht="17">
+      <c r="A919" t="s">
+        <v>3</v>
+      </c>
+      <c r="B919" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C919" s="19" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3" ht="17">
+      <c r="A920" t="s">
+        <v>3</v>
+      </c>
+      <c r="B920" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C920" s="19" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3" ht="17">
+      <c r="A921" t="s">
+        <v>3</v>
+      </c>
+      <c r="B921" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C921" s="19" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3" ht="17">
+      <c r="A922" t="s">
+        <v>3</v>
+      </c>
+      <c r="B922" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C922" s="19" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3" ht="17">
+      <c r="A923" t="s">
+        <v>3</v>
+      </c>
+      <c r="B923" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C923" s="19" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3" ht="17">
+      <c r="A924" t="s">
+        <v>3</v>
+      </c>
+      <c r="B924" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C924" s="19" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3" ht="17">
+      <c r="A925" t="s">
+        <v>3</v>
+      </c>
+      <c r="B925" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C925" s="19" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3" ht="17">
+      <c r="A926" t="s">
+        <v>3</v>
+      </c>
+      <c r="B926" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C926" s="19" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3" ht="17">
+      <c r="A927" t="s">
+        <v>3</v>
+      </c>
+      <c r="B927" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C927" s="19" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3" ht="17">
+      <c r="A928" t="s">
+        <v>3</v>
+      </c>
+      <c r="B928" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C928" s="19" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3" ht="17">
+      <c r="A929" t="s">
+        <v>3</v>
+      </c>
+      <c r="B929" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C929" s="19" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3" ht="17">
+      <c r="A930" t="s">
+        <v>3</v>
+      </c>
+      <c r="B930" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C930" s="19" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3" ht="17">
+      <c r="A931" t="s">
+        <v>3</v>
+      </c>
+      <c r="B931" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C931" s="19" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3" ht="17">
+      <c r="A932" t="s">
+        <v>3</v>
+      </c>
+      <c r="B932" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C932" s="19" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3" ht="17">
+      <c r="A933" t="s">
+        <v>3</v>
+      </c>
+      <c r="B933" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C933" s="19" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3" ht="17">
+      <c r="A934" t="s">
+        <v>3</v>
+      </c>
+      <c r="B934" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C934" s="19" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3" ht="17">
+      <c r="A935" t="s">
+        <v>3</v>
+      </c>
+      <c r="B935" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C935" s="19" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3" ht="17">
+      <c r="A936" t="s">
+        <v>3</v>
+      </c>
+      <c r="B936" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C936" s="19" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3" ht="17">
+      <c r="A937" t="s">
+        <v>3</v>
+      </c>
+      <c r="B937" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C937" s="19" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3" ht="17">
+      <c r="A938" t="s">
+        <v>3</v>
+      </c>
+      <c r="B938" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C938" s="19" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3" ht="17">
+      <c r="A939" t="s">
+        <v>3</v>
+      </c>
+      <c r="B939" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C939" s="19" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3" ht="17">
+      <c r="A940" t="s">
+        <v>3</v>
+      </c>
+      <c r="B940" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C940" s="19" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3" ht="17">
+      <c r="A941" t="s">
+        <v>3</v>
+      </c>
+      <c r="B941" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C941" s="19" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3" ht="17">
+      <c r="A942" t="s">
+        <v>3</v>
+      </c>
+      <c r="B942" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C942" s="19" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3" ht="17">
+      <c r="A943" t="s">
+        <v>3</v>
+      </c>
+      <c r="B943" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C943" s="19" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3" ht="17">
+      <c r="A944" t="s">
+        <v>3</v>
+      </c>
+      <c r="B944" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C944" s="19" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3" ht="17">
+      <c r="A945" t="s">
+        <v>3</v>
+      </c>
+      <c r="B945" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C945" s="19" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3" ht="17">
+      <c r="A946" t="s">
+        <v>3</v>
+      </c>
+      <c r="B946" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C946" s="19" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3" ht="17">
+      <c r="A947" t="s">
+        <v>3</v>
+      </c>
+      <c r="B947" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C947" s="19" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3" ht="17">
+      <c r="A948" t="s">
+        <v>3</v>
+      </c>
+      <c r="B948" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C948" s="19" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="949" spans="1:3" ht="17">
+      <c r="A949" t="s">
+        <v>3</v>
+      </c>
+      <c r="B949" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C949" s="19" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="950" spans="1:3" ht="17">
+      <c r="A950" t="s">
+        <v>3</v>
+      </c>
+      <c r="B950" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C950" s="19" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="951" spans="1:3" ht="17">
+      <c r="A951" t="s">
+        <v>3</v>
+      </c>
+      <c r="B951" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C951" s="19" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="952" spans="1:3" ht="17">
+      <c r="A952" t="s">
+        <v>3</v>
+      </c>
+      <c r="B952" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C952" s="19" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="953" spans="1:3" ht="17">
+      <c r="A953" t="s">
+        <v>3</v>
+      </c>
+      <c r="B953" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C953" s="19" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="954" spans="1:3" ht="17">
+      <c r="A954" t="s">
+        <v>3</v>
+      </c>
+      <c r="B954" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C954" s="19" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="955" spans="1:3" ht="17">
+      <c r="A955" t="s">
+        <v>3</v>
+      </c>
+      <c r="B955" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C955" s="19" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="956" spans="1:3" ht="17">
+      <c r="A956" t="s">
+        <v>3</v>
+      </c>
+      <c r="B956" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C956" s="19" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="957" spans="1:3" ht="17">
+      <c r="A957" t="s">
+        <v>3</v>
+      </c>
+      <c r="B957" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C957" s="19" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3" ht="17">
+      <c r="A958" t="s">
+        <v>3</v>
+      </c>
+      <c r="B958" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C958" s="19" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="959" spans="1:3" ht="17">
+      <c r="A959" t="s">
+        <v>3</v>
+      </c>
+      <c r="B959" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C959" s="19" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="960" spans="1:3" ht="17">
+      <c r="A960" t="s">
+        <v>3</v>
+      </c>
+      <c r="B960" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C960" s="19" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="961" spans="1:3" ht="17">
+      <c r="A961" t="s">
+        <v>3</v>
+      </c>
+      <c r="B961" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C961" s="19" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="962" spans="1:3" ht="17">
+      <c r="A962" t="s">
+        <v>3</v>
+      </c>
+      <c r="B962" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C962" s="19" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="963" spans="1:3" ht="17">
+      <c r="A963" t="s">
+        <v>3</v>
+      </c>
+      <c r="B963" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C963" s="19" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="964" spans="1:3" ht="17">
+      <c r="A964" t="s">
+        <v>3</v>
+      </c>
+      <c r="B964" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C964" s="19" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="965" spans="1:3" ht="17">
+      <c r="A965" t="s">
+        <v>3</v>
+      </c>
+      <c r="B965" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C965" s="19" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="966" spans="1:3" ht="17">
+      <c r="A966" t="s">
+        <v>3</v>
+      </c>
+      <c r="B966" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C966" s="19" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="967" spans="1:3" ht="17">
+      <c r="A967" t="s">
+        <v>3</v>
+      </c>
+      <c r="B967" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C967" s="19" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="968" spans="1:3" ht="17">
+      <c r="A968" t="s">
+        <v>3</v>
+      </c>
+      <c r="B968" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C968" s="19" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="969" spans="1:3" ht="17">
+      <c r="A969" t="s">
+        <v>3</v>
+      </c>
+      <c r="B969" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C969" s="19" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="970" spans="1:3" ht="17">
+      <c r="A970" t="s">
+        <v>3</v>
+      </c>
+      <c r="B970" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C970" s="19" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="971" spans="1:3" ht="17">
+      <c r="A971" t="s">
+        <v>3</v>
+      </c>
+      <c r="B971" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C971" s="19" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="972" spans="1:3" ht="17">
+      <c r="A972" t="s">
+        <v>3</v>
+      </c>
+      <c r="B972" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C972" s="19" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="973" spans="1:3" ht="17">
+      <c r="A973" t="s">
+        <v>3</v>
+      </c>
+      <c r="B973" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C973" s="19" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="974" spans="1:3" ht="17">
+      <c r="A974" t="s">
+        <v>3</v>
+      </c>
+      <c r="B974" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C974" s="19" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="975" spans="1:3" ht="17">
+      <c r="A975" t="s">
+        <v>3</v>
+      </c>
+      <c r="B975" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C975" s="19" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="976" spans="1:3" ht="17">
+      <c r="A976" t="s">
+        <v>3</v>
+      </c>
+      <c r="B976" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C976" s="19" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="977" spans="1:3" ht="17">
+      <c r="A977" t="s">
+        <v>3</v>
+      </c>
+      <c r="B977" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C977" s="19" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="978" spans="1:3" ht="17">
+      <c r="A978" t="s">
+        <v>3</v>
+      </c>
+      <c r="B978" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C978" s="19" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="979" spans="1:3" ht="17">
+      <c r="A979" t="s">
+        <v>3</v>
+      </c>
+      <c r="B979" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C979" s="19" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="980" spans="1:3" ht="17">
+      <c r="A980" t="s">
+        <v>3</v>
+      </c>
+      <c r="B980" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C980" s="19" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="981" spans="1:3" ht="17">
+      <c r="A981" t="s">
+        <v>3</v>
+      </c>
+      <c r="B981" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C981" s="19" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="982" spans="1:3" ht="17">
+      <c r="A982" t="s">
+        <v>3</v>
+      </c>
+      <c r="B982" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C982" s="19" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="983" spans="1:3" ht="17">
+      <c r="A983" t="s">
+        <v>3</v>
+      </c>
+      <c r="B983" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C983" s="19" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="984" spans="1:3" ht="17">
+      <c r="A984" t="s">
+        <v>3</v>
+      </c>
+      <c r="B984" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C984" s="19" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="985" spans="1:3" ht="17">
+      <c r="A985" t="s">
+        <v>3</v>
+      </c>
+      <c r="B985" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C985" s="19" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="986" spans="1:3" ht="17">
+      <c r="A986" t="s">
+        <v>3</v>
+      </c>
+      <c r="B986" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C986" s="19" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="987" spans="1:3" ht="17">
+      <c r="A987" t="s">
+        <v>3</v>
+      </c>
+      <c r="B987" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C987" s="19" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="988" spans="1:3" ht="17">
+      <c r="A988" t="s">
+        <v>3</v>
+      </c>
+      <c r="B988" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C988" s="19" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="989" spans="1:3" ht="17">
+      <c r="A989" t="s">
+        <v>3</v>
+      </c>
+      <c r="B989" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C989" s="19" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="990" spans="1:3" ht="17">
+      <c r="A990" t="s">
+        <v>3</v>
+      </c>
+      <c r="B990" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C990" s="19" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="991" spans="1:3" ht="17">
+      <c r="A991" t="s">
+        <v>3</v>
+      </c>
+      <c r="B991" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C991" s="19" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="992" spans="1:3" ht="17">
+      <c r="A992" t="s">
+        <v>3</v>
+      </c>
+      <c r="B992" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C992" s="19" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="993" spans="1:3" ht="17">
+      <c r="A993" t="s">
+        <v>3</v>
+      </c>
+      <c r="B993" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C993" s="19" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="994" spans="1:3" ht="17">
+      <c r="A994" t="s">
+        <v>3</v>
+      </c>
+      <c r="B994" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C994" s="19" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="995" spans="1:3" ht="17">
+      <c r="A995" t="s">
+        <v>3</v>
+      </c>
+      <c r="B995" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C995" s="19" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="996" spans="1:3" ht="17">
+      <c r="A996" t="s">
+        <v>3</v>
+      </c>
+      <c r="B996" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C996" s="19" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="997" spans="1:3" ht="17">
+      <c r="A997" t="s">
+        <v>3</v>
+      </c>
+      <c r="B997" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C997" s="19" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="998" spans="1:3" ht="17">
+      <c r="A998" t="s">
+        <v>3</v>
+      </c>
+      <c r="B998" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C998" s="19" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="999" spans="1:3" ht="17">
+      <c r="A999" t="s">
+        <v>3</v>
+      </c>
+      <c r="B999" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C999" s="19" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:3" ht="17">
+      <c r="A1000" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1000" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1000" s="19" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:3" ht="17">
+      <c r="A1001" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1001" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1001" s="19" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:3" ht="17">
+      <c r="A1002" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1002" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1002" s="19" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:3" ht="17">
+      <c r="A1003" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1003" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1003" s="19" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:3" ht="17">
+      <c r="A1004" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1004" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1004" s="19" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:3" ht="17">
+      <c r="A1005" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1005" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1005" s="19" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:3" ht="17">
+      <c r="A1006" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1006" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1006" s="19" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:3" ht="17">
+      <c r="A1007" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1007" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1007" s="19" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:3" ht="17">
+      <c r="A1008" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1008" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1008" s="19" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:3" ht="17">
+      <c r="A1009" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1009" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1009" s="19" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:3" ht="17">
+      <c r="A1010" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1010" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1010" s="19" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:3" ht="17">
+      <c r="A1011" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1011" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1011" s="19" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:3" ht="17">
+      <c r="A1012" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1012" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1012" s="19" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:3" ht="17">
+      <c r="A1013" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1013" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1013" s="19" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:3" ht="17">
+      <c r="A1014" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1014" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1014" s="19" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:3" ht="17">
+      <c r="A1015" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1015" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1015" s="19" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:3" ht="17">
+      <c r="A1016" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1016" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1016" s="19" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:3" ht="17">
+      <c r="A1017" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1017" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1017" s="19" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:3" ht="17">
+      <c r="A1018" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1018" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1018" s="19" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:3" ht="17">
+      <c r="A1019" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1019" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1019" s="19" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:3" ht="17">
+      <c r="A1020" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1020" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1020" s="19" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:3" ht="17">
+      <c r="A1021" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1021" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1021" s="19" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:3" ht="17">
+      <c r="A1022" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1022" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1022" s="19" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:3" ht="17">
+      <c r="A1023" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1023" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1023" s="19" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:3" ht="17">
+      <c r="A1024" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1024" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1024" s="19" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:3" ht="17">
+      <c r="A1025" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1025" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1025" s="19" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:3" ht="17">
+      <c r="A1026" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1026" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1026" s="19" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:3" ht="17">
+      <c r="A1027" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1027" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1027" s="19" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:3" ht="17">
+      <c r="A1028" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1028" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1028" s="19" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:3" ht="17">
+      <c r="A1029" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1029" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1029" s="19" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:3" ht="17">
+      <c r="A1030" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1030" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1030" s="19" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:3" ht="17">
+      <c r="A1031" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1031" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1031" s="19" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:3" ht="17">
+      <c r="A1032" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1032" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1032" s="19" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:3" ht="17">
+      <c r="A1033" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1033" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1033" s="19" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:3" ht="17">
+      <c r="A1034" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1034" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1034" s="19" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:3" ht="17">
+      <c r="A1035" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1035" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1035" s="19" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:3" ht="17">
+      <c r="A1036" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1036" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1036" s="19" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:3" ht="17">
+      <c r="A1037" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1037" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1037" s="19" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:3" ht="17">
+      <c r="A1038" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1038" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1038" s="19" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:3" ht="17">
+      <c r="A1039" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1039" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1039" s="19" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:3" ht="17">
+      <c r="A1040" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1040" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1040" s="19" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:3" ht="17">
+      <c r="A1041" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1041" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1041" s="19" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:3" ht="17">
+      <c r="A1042" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1042" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1042" s="19" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:3" ht="17">
+      <c r="A1043" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1043" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1043" s="19" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:3" ht="17">
+      <c r="A1044" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1044" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1044" s="19" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:3" ht="17">
+      <c r="A1045" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1045" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1045" s="19" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:3" ht="17">
+      <c r="A1046" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1046" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1046" s="19" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:3" ht="17">
+      <c r="A1047" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1047" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1047" s="19" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:3" ht="17">
+      <c r="A1048" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1048" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1048" s="19" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:3" ht="17">
+      <c r="A1049" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1049" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1049" s="19" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:3" ht="17">
+      <c r="A1050" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1050" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1050" s="19" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:3" ht="17">
+      <c r="A1051" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1051" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1051" s="19" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:3" ht="17">
+      <c r="A1052" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1052" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1052" s="19" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:3" ht="17">
+      <c r="A1053" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1053" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1053" s="19" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:3" ht="17">
+      <c r="A1054" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1054" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1054" s="19" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:3" ht="17">
+      <c r="A1055" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1055" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1055" s="19" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:3" ht="17">
+      <c r="A1056" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1056" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1056" s="19" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:3" ht="17">
+      <c r="A1057" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1057" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1057" s="19" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:3" ht="17">
+      <c r="A1058" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1058" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1058" s="19" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:3" ht="17">
+      <c r="A1059" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1059" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1059" s="19" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:3" ht="17">
+      <c r="A1060" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1060" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1060" s="19" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:3" ht="17">
+      <c r="A1061" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1061" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1061" s="19" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:3" ht="17">
+      <c r="A1062" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1062" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1062" s="19" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:3" ht="17">
+      <c r="A1063" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1063" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1063" s="19" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:3" ht="17">
+      <c r="A1064" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1064" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1064" s="19" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:3" ht="17">
+      <c r="A1065" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1065" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1065" s="19" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:3" ht="17">
+      <c r="A1066" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1066" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1066" s="19" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:3" ht="17">
+      <c r="A1067" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1067" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1067" s="19" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:3" ht="17">
+      <c r="A1068" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1068" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1068" s="19" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:3" ht="17">
+      <c r="A1069" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1069" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1069" s="19" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:3" ht="17">
+      <c r="A1070" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1070" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1070" s="19" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:3" ht="17">
+      <c r="A1071" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1071" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1071" s="19" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:3" ht="17">
+      <c r="A1072" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1072" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1072" s="19" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:3" ht="17">
+      <c r="A1073" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1073" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1073" s="19" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:3" ht="17">
+      <c r="A1074" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1074" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1074" s="19" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:3" ht="17">
+      <c r="A1075" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1075" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1075" s="19" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:3" ht="17">
+      <c r="A1076" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1076" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1076" s="19" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:3" ht="17">
+      <c r="A1077" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1077" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1077" s="19" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:3" ht="17">
+      <c r="A1078" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1078" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1078" s="19" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:3" ht="17">
+      <c r="A1079" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1079" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1079" s="19" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:3" ht="17">
+      <c r="A1080" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1080" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1080" s="19" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:3" ht="17">
+      <c r="A1081" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1081" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1081" s="19" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:3" ht="17">
+      <c r="A1082" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1082" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1082" s="19" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:3" ht="17">
+      <c r="A1083" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1083" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1083" s="19" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:3" ht="17">
+      <c r="A1084" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1084" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1084" s="19" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:3" ht="17">
+      <c r="A1085" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1085" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1085" s="19" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:3" ht="17">
+      <c r="A1086" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1086" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1086" s="19" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:3" ht="17">
+      <c r="A1087" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1087" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1087" s="19" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:3" ht="17">
+      <c r="A1088" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1088" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1088" s="19" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:3" ht="17">
+      <c r="A1089" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1089" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1089" s="19" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:3" ht="17">
+      <c r="A1090" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1090" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1090" s="19" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:3" ht="17">
+      <c r="A1091" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1091" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1091" s="19" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:3" ht="17">
+      <c r="A1092" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1092" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1092" s="19" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:3" ht="17">
+      <c r="A1093" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1093" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1093" s="19" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:3" ht="17">
+      <c r="A1094" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1094" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1094" s="19" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:3" ht="17">
+      <c r="A1095" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1095" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1095" s="19" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:3" ht="17">
+      <c r="A1096" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1096" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1096" s="19" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:3" ht="17">
+      <c r="A1097" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1097" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1097" s="19" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:3" ht="17">
+      <c r="A1098" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1098" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1098" s="19" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:3" ht="17">
+      <c r="A1099" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1099" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1099" s="19" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:3" ht="17">
+      <c r="A1100" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1100" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1100" s="19" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:3" ht="17">
+      <c r="A1101" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1101" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1101" s="19" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:3" ht="17">
+      <c r="A1102" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1102" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1102" s="19" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:3" ht="17">
+      <c r="A1103" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1103" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1103" s="19" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:3" ht="17">
+      <c r="A1104" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1104" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1104" s="19" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:3" ht="17">
+      <c r="A1105" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1105" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1105" s="19" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:3" ht="17">
+      <c r="A1106" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1106" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1106" s="19" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:3" ht="17">
+      <c r="A1107" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1107" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1107" s="19" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:3" ht="17">
+      <c r="A1108" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1108" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1108" s="19" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:3" ht="17">
+      <c r="A1109" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1109" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1109" s="19" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:3" ht="17">
+      <c r="A1110" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1110" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1110" s="19" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:3" ht="17">
+      <c r="A1111" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1111" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1111" s="19" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:3" ht="17">
+      <c r="A1112" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1112" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1112" s="19" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:3" ht="17">
+      <c r="A1113" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1113" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1113" s="19" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:3" ht="17">
+      <c r="A1114" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1114" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1114" s="19" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:3" ht="17">
+      <c r="A1115" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1115" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1115" s="19" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:3" ht="17">
+      <c r="A1116" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1116" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1116" s="19" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:3" ht="17">
+      <c r="A1117" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1117" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1117" s="19" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:3" ht="17">
+      <c r="A1118" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1118" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1118" s="19" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:3" ht="17">
+      <c r="A1119" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1119" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1119" s="19" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:3" ht="17">
+      <c r="A1120" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1120" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1120" s="19" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:3" ht="17">
+      <c r="A1121" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1121" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1121" s="19" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:3" ht="17">
+      <c r="A1122" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1122" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1122" s="19" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:3" ht="17">
+      <c r="A1123" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1123" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1123" s="19" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:3" ht="17">
+      <c r="A1124" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1124" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1124" s="19" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:3" ht="17">
+      <c r="A1125" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1125" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1125" s="19" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:3" ht="17">
+      <c r="A1126" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1126" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1126" s="19" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:3" ht="17">
+      <c r="A1127" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1127" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1127" s="19" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:3" ht="17">
+      <c r="A1128" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1128" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1128" s="19" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:3" ht="17">
+      <c r="A1129" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1129" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1129" s="19" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:3" ht="17">
+      <c r="A1130" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1130" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1130" s="19" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:3" ht="17">
+      <c r="A1131" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1131" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1131" s="19" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:3" ht="17">
+      <c r="A1132" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1132" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1132" s="19" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:3" ht="17">
+      <c r="A1133" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1133" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1133" s="19" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:3" ht="17">
+      <c r="A1134" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1134" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1134" s="19" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:3" ht="17">
+      <c r="A1135" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1135" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1135" s="19" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:3" ht="17">
+      <c r="A1136" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1136" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1136" s="19" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:3" ht="17">
+      <c r="A1137" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1137" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1137" s="19" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:3" ht="17">
+      <c r="A1138" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1138" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1138" s="19" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:3" ht="17">
+      <c r="A1139" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1139" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1139" s="19" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:3" ht="17">
+      <c r="A1140" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1140" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1140" s="19" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:3" ht="17">
+      <c r="A1141" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1141" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1141" s="19" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:3" ht="17">
+      <c r="A1142" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1142" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1142" s="19" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:3" ht="17">
+      <c r="A1143" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1143" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1143" s="19" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:3" ht="17">
+      <c r="A1144" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1144" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1144" s="19" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:3" ht="17">
+      <c r="A1145" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1145" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1145" s="19" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:3" ht="17">
+      <c r="A1146" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1146" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1146" s="19" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:3" ht="17">
+      <c r="A1147" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1147" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1147" s="19" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:3" ht="17">
+      <c r="A1148" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1148" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1148" s="19" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:3" ht="17">
+      <c r="A1149" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1149" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1149" s="19" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:3" ht="17">
+      <c r="A1150" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1150" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1150" s="19" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:3" ht="17">
+      <c r="A1151" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1151" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1151" s="19" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:3" ht="17">
+      <c r="A1152" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1152" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1152" s="19" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:3" ht="17">
+      <c r="A1153" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1153" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1153" s="19" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:3" ht="17">
+      <c r="A1154" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1154" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1154" s="19" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:3" ht="17">
+      <c r="A1155" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1155" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1155" s="19" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:3" ht="17">
+      <c r="A1156" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1156" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1156" s="19" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:3" ht="17">
+      <c r="A1157" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1157" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1157" s="19" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:3" ht="17">
+      <c r="A1158" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1158" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1158" s="19" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:3" ht="17">
+      <c r="A1159" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1159" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1159" s="19" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:3" ht="17">
+      <c r="A1160" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1160" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1160" s="19" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:3" ht="17">
+      <c r="A1161" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1161" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1161" s="19" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:3" ht="17">
+      <c r="A1162" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1162" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1162" s="19" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:3" ht="17">
+      <c r="A1163" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1163" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1163" s="19" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:3" ht="17">
+      <c r="A1164" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1164" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1164" s="19" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:3" ht="17">
+      <c r="A1165" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1165" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1165" s="19" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:3" ht="17">
+      <c r="A1166" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1166" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1166" s="19" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:3" ht="17">
+      <c r="A1167" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1167" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1167" s="19" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:3" ht="17">
+      <c r="A1168" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1168" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1168" s="19" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:3" ht="17">
+      <c r="A1169" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1169" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1169" s="19" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:3" ht="17">
+      <c r="A1170" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1170" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1170" s="19" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:3" ht="17">
+      <c r="A1171" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1171" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1171" s="19" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:3" ht="17">
+      <c r="A1172" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1172" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1172" s="19" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:3" ht="17">
+      <c r="A1173" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1173" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1173" s="19" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:3" ht="17">
+      <c r="A1174" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1174" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1174" s="19" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:3" ht="17">
+      <c r="A1175" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1175" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1175" s="19" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:3" ht="17">
+      <c r="A1176" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1176" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1176" s="19" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:3" ht="17">
+      <c r="A1177" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1177" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1177" s="19" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:3" ht="17">
+      <c r="A1178" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1178" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1178" s="19" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:3" ht="17">
+      <c r="A1179" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1179" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1179" s="19" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:3" ht="17">
+      <c r="A1180" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1180" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1180" s="19" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:3" ht="17">
+      <c r="A1181" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1181" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1181" s="19" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:3" ht="17">
+      <c r="A1182" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1182" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1182" s="19" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:3" ht="17">
+      <c r="A1183" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1183" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1183" s="19" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:3" ht="17">
+      <c r="A1184" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1184" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1184" s="19" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:3" ht="17">
+      <c r="A1185" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1185" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1185" s="19" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:3" ht="17">
+      <c r="A1186" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1186" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1186" s="19" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:3" ht="17">
+      <c r="A1187" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1187" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1187" s="19" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:3" ht="17">
+      <c r="A1188" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1188" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1188" s="19" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:3" ht="17">
+      <c r="A1189" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1189" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1189" s="19" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:3" ht="17">
+      <c r="A1190" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1190" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1190" s="19" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:3" ht="17">
+      <c r="A1191" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1191" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1191" s="19" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:3" ht="17">
+      <c r="A1192" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1192" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1192" s="19" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:3" ht="17">
+      <c r="A1193" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1193" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1193" s="19" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:3" ht="17">
+      <c r="A1194" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1194" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1194" s="19" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:3" ht="17">
+      <c r="A1195" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1195" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1195" s="19" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:3" ht="17">
+      <c r="A1196" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1196" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1196" s="19" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:3" ht="17">
+      <c r="A1197" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1197" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1197" s="19" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:3" ht="17">
+      <c r="A1198" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1198" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1198" s="19" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:3" ht="17">
+      <c r="A1199" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1199" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1199" s="19" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:3" ht="17">
+      <c r="A1200" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1200" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1200" s="19" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:3" ht="17">
+      <c r="A1201" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1201" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1201" s="19" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:3" ht="17">
+      <c r="A1202" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1202" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1202" s="19" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:3" ht="17">
+      <c r="A1203" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1203" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1203" s="19" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:3" ht="17">
+      <c r="A1204" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1204" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1204" s="19" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:3" ht="17">
+      <c r="A1205" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1205" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1205" s="19" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:3" ht="17">
+      <c r="A1206" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1206" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1206" s="19" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:3" ht="17">
+      <c r="A1207" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1207" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1207" s="19" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:3" ht="17">
+      <c r="A1208" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1208" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1208" s="19" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:3" ht="17">
+      <c r="A1209" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1209" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1209" s="19" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:3" ht="17">
+      <c r="A1210" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1210" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1210" s="19" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:3" ht="17">
+      <c r="A1211" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1211" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1211" s="19" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:3" ht="17">
+      <c r="A1212" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1212" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1212" s="19" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:3" ht="17">
+      <c r="A1213" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1213" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1213" s="19" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:3" ht="17">
+      <c r="A1214" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1214" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1214" s="19" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:3" ht="17">
+      <c r="A1215" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1215" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1215" s="19" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:3" ht="17">
+      <c r="A1216" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1216" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1216" s="19" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:3" ht="17">
+      <c r="A1217" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1217" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1217" s="19" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:3" ht="17">
+      <c r="A1218" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1218" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1218" s="19" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:3" ht="17">
+      <c r="A1219" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1219" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1219" s="19" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:3" ht="17">
+      <c r="A1220" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1220" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1220" s="19" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:3" ht="17">
+      <c r="A1221" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1221" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1221" s="19" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:3" ht="17">
+      <c r="A1222" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1222" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1222" s="19" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:3" ht="17">
+      <c r="A1223" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1223" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1223" s="19" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:3" ht="17">
+      <c r="A1224" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1224" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1224" s="19" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:3" ht="17">
+      <c r="A1225" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1225" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1225" s="19" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:3" ht="17">
+      <c r="A1226" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1226" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1226" s="19" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:3" ht="17">
+      <c r="A1227" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1227" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1227" s="19" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:3" ht="17">
+      <c r="A1228" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1228" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1228" s="19" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:3" ht="17">
+      <c r="A1229" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1229" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1229" s="19" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:3" ht="17">
+      <c r="A1230" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1230" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1230" s="19" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:3" ht="17">
+      <c r="A1231" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1231" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1231" s="19" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:3" ht="17">
+      <c r="A1232" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1232" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1232" s="19" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:3" ht="17">
+      <c r="A1233" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1233" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1233" s="19" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:3" ht="17">
+      <c r="A1234" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1234" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1234" s="19" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:3" ht="17">
+      <c r="A1235" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1235" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1235" s="19" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:3" ht="17">
+      <c r="A1236" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1236" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1236" s="19" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:3" ht="17">
+      <c r="A1237" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1237" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1237" s="19" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:3" ht="17">
+      <c r="A1238" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1238" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1238" s="19" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:3" ht="17">
+      <c r="A1239" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1239" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1239" s="19" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:3" ht="17">
+      <c r="A1240" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1240" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1240" s="19" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:3" ht="17">
+      <c r="A1241" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1241" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1241" s="19" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:3" ht="17">
+      <c r="A1242" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1242" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1242" s="19" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:3" ht="17">
+      <c r="A1243" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1243" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1243" s="19" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:3" ht="17">
+      <c r="A1244" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1244" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1244" s="19" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:3" ht="17">
+      <c r="A1245" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1245" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1245" s="19" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:3" ht="17">
+      <c r="A1246" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1246" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1246" s="19" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:3" ht="17">
+      <c r="A1247" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1247" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1247" s="19" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:3" ht="17">
+      <c r="A1248" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1248" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1248" s="19" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:3" ht="17">
+      <c r="A1249" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1249" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1249" s="19" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:3" ht="17">
+      <c r="A1250" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1250" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1250" s="19" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:3" ht="17">
+      <c r="A1251" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1251" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1251" s="19" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:3" ht="17">
+      <c r="A1252" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1252" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1252" s="19" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:3" ht="17">
+      <c r="A1253" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1253" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1253" s="19" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:3" ht="17">
+      <c r="A1254" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1254" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1254" s="19" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:3" ht="17">
+      <c r="A1255" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1255" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1255" s="19" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:3" ht="17">
+      <c r="A1256" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1256" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1256" s="19" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:3" ht="17">
+      <c r="A1257" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1257" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1257" s="19" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:3" ht="17">
+      <c r="A1258" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1258" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1258" s="19" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:3" ht="17">
+      <c r="A1259" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1259" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1259" s="19" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:3" ht="17">
+      <c r="A1260" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1260" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1260" s="19" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:3" ht="17">
+      <c r="A1261" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1261" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1261" s="19" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:3" ht="17">
+      <c r="A1262" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1262" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1262" s="19" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:3" ht="17">
+      <c r="A1263" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1263" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1263" s="19" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:3" ht="17">
+      <c r="A1264" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1264" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1264" s="19" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:3" ht="17">
+      <c r="A1265" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1265" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1265" s="19" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:3" ht="17">
+      <c r="A1266" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1266" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1266" s="19" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:3" ht="17">
+      <c r="A1267" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1267" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1267" s="19" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:3" ht="17">
+      <c r="A1268" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1268" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1268" s="19" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:3" ht="17">
+      <c r="A1269" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1269" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1269" s="19" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:3" ht="17">
+      <c r="A1270" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1270" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1270" s="19" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:3" ht="17">
+      <c r="A1271" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1271" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1271" s="19" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:3" ht="17">
+      <c r="A1272" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1272" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1272" s="19" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:3" ht="17">
+      <c r="A1273" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1273" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1273" s="19" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:3" ht="17">
+      <c r="A1274" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1274" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1274" s="19" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:3" ht="17">
+      <c r="A1275" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1275" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1275" s="19" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:3" ht="17">
+      <c r="A1276" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1276" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1276" s="19" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:3" ht="17">
+      <c r="A1277" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1277" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1277" s="19" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:3" ht="17">
+      <c r="A1278" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1278" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1278" s="19" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:3" ht="17">
+      <c r="A1279" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1279" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1279" s="19" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:3" ht="17">
+      <c r="A1280" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1280" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1280" s="19" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:3" ht="17">
+      <c r="A1281" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1281" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1281" s="19" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:3" ht="17">
+      <c r="A1282" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1282" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1282" s="19" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:3" ht="17">
+      <c r="A1283" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1283" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1283" s="19" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:3" ht="17">
+      <c r="A1284" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1284" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1284" s="19" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:3" ht="17">
+      <c r="A1285" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1285" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1285" s="19" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:3" ht="17">
+      <c r="A1286" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1286" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1286" s="19" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:3" ht="17">
+      <c r="A1287" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1287" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1287" s="19" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:3" ht="17">
+      <c r="A1288" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1288" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1288" s="19" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:3" ht="17">
+      <c r="A1289" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1289" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1289" s="19" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:3" ht="17">
+      <c r="A1290" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1290" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1290" s="19" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:3" ht="17">
+      <c r="A1291" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1291" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1291" s="19" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:3" ht="17">
+      <c r="A1292" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1292" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1292" s="19" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:3" ht="17">
+      <c r="A1293" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1293" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1293" s="19" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:3" ht="17">
+      <c r="A1294" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1294" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1294" s="19" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:3" ht="17">
+      <c r="A1295" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1295" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1295" s="19" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:3" ht="17">
+      <c r="A1296" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1296" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1296" s="19" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:3" ht="17">
+      <c r="A1297" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1297" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1297" s="19" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:3" ht="17">
+      <c r="A1298" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1298" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1298" s="19" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:3" ht="17">
+      <c r="A1299" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1299" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1299" s="19" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:3" ht="17">
+      <c r="A1300" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1300" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1300" s="19" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:3" ht="17">
+      <c r="A1301" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1301" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1301" s="19" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:3" ht="17">
+      <c r="A1302" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1302" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1302" s="19" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:3" ht="17">
+      <c r="A1303" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1303" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1303" s="19" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:3" ht="17">
+      <c r="A1304" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1304" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1304" s="19" t="s">
+        <v>1651</v>
       </c>
     </row>
   </sheetData>
@@ -17810,8 +25326,8 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
       <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9">
